--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,6 +636,22 @@
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-installation</t>
+  </si>
+  <si>
+    <t>as-ext-installation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation}
+</t>
+  </si>
+  <si>
+    <t>AS Installation Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les dates d'installation des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>
@@ -1720,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL70"/>
+  <dimension ref="A1:AL71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.46484375" customWidth="true" bestFit="true"/>
@@ -3821,11 +3837,13 @@
         <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3835,29 +3853,25 @@
         <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3893,19 +3907,19 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3920,7 +3934,7 @@
         <v>115</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -3935,7 +3949,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3948,22 +3962,26 @@
         <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
@@ -3999,10 +4017,10 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
@@ -4011,7 +4029,7 @@
         <v>113</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4023,25 +4041,23 @@
         <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
@@ -4050,10 +4066,10 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>75</v>
@@ -4062,13 +4078,13 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4107,19 +4123,19 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4134,20 +4150,22 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
@@ -4159,22 +4177,22 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4225,44 +4243,44 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
@@ -4274,17 +4292,15 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4321,34 +4337,34 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4356,46 +4372,44 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4419,46 +4433,46 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
@@ -4466,10 +4480,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4486,25 +4500,25 @@
         <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4529,13 +4543,13 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>149</v>
+        <v>230</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4553,7 +4567,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4568,7 +4582,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4576,10 +4590,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4587,7 +4601,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>84</v>
@@ -4602,19 +4616,19 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4624,10 +4638,10 @@
         <v>75</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>246</v>
+        <v>75</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4639,13 +4653,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4663,7 +4677,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4678,7 +4692,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4686,10 +4700,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4697,7 +4711,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>84</v>
@@ -4712,18 +4726,20 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4732,10 +4748,10 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -4771,7 +4787,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4786,7 +4802,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4794,10 +4810,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4820,16 +4836,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4843,7 +4859,7 @@
         <v>75</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>75</v>
@@ -4879,7 +4895,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4891,10 +4907,10 @@
         <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>265</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4902,10 +4918,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4928,16 +4944,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4987,7 +5003,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4999,10 +5015,10 @@
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -5010,10 +5026,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5030,30 +5046,28 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>75</v>
       </c>
@@ -5097,7 +5111,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5109,21 +5123,21 @@
         <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>283</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5137,31 +5151,33 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q32" s="2"/>
+      <c r="Q32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="R32" t="s" s="2">
         <v>75</v>
       </c>
@@ -5205,7 +5221,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5217,32 +5233,32 @@
         <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>75</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>85</v>
@@ -5254,16 +5270,16 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5289,11 +5305,13 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>295</v>
+        <v>75</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5311,37 +5329,37 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5351,7 +5369,7 @@
         <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -5360,16 +5378,16 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5395,11 +5413,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5417,7 +5435,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5432,32 +5450,32 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>75</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -5466,16 +5484,16 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5501,7 +5519,7 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
@@ -5523,7 +5541,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5538,7 +5556,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5546,10 +5564,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5563,7 +5581,7 @@
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5572,7 +5590,7 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>311</v>
@@ -5581,7 +5599,7 @@
         <v>312</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5607,13 +5625,11 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5631,7 +5647,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5643,21 +5659,21 @@
         <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5680,16 +5696,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>100</v>
+        <v>315</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5739,25 +5755,25 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -5893,19 +5909,19 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5970,7 +5986,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5978,10 +5994,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6001,19 +6017,19 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6063,7 +6079,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6075,10 +6091,10 @@
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>337</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6086,10 +6102,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6109,19 +6125,19 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6171,22 +6187,22 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6194,10 +6210,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6220,16 +6236,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6279,7 +6295,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6291,7 +6307,7 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>274</v>
+        <v>349</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>350</v>
@@ -6328,7 +6344,7 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>352</v>
@@ -6363,13 +6379,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>355</v>
+        <v>75</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6399,10 +6415,10 @@
         <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6410,10 +6426,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6436,15 +6452,17 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6469,13 +6487,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>75</v>
+        <v>358</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6493,7 +6511,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6508,7 +6526,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>104</v>
+        <v>361</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6516,10 +6534,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6530,7 +6548,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6542,13 +6560,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>101</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6599,19 +6617,19 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>104</v>
@@ -6622,21 +6640,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
@@ -6648,17 +6666,15 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6695,34 +6711,34 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6730,14 +6746,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6750,26 +6766,24 @@
         <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -6805,19 +6819,19 @@
         <v>75</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>114</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6847,37 +6861,39 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6901,10 +6917,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6925,22 +6941,22 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>356</v>
+        <v>98</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6948,10 +6964,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6974,16 +6990,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>327</v>
+        <v>237</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>375</v>
+        <v>307</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7009,10 +7025,10 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>75</v>
@@ -7033,7 +7049,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7048,7 +7064,7 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -7070,7 +7086,7 @@
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -7082,7 +7098,7 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>232</v>
+        <v>332</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>378</v>
@@ -7117,13 +7133,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>381</v>
+        <v>75</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7147,7 +7163,7 @@
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>96</v>
@@ -7156,7 +7172,7 @@
         <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7164,10 +7180,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7178,10 +7194,10 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>75</v>
@@ -7190,16 +7206,16 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7225,11 +7241,13 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7247,7 +7265,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7262,7 +7280,7 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7284,10 +7302,10 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
@@ -7296,7 +7314,7 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>390</v>
@@ -7331,13 +7349,11 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>174</v>
+        <v>393</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7370,7 +7386,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7404,7 +7420,7 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>395</v>
@@ -7413,7 +7429,7 @@
         <v>396</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7439,13 +7455,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>397</v>
+        <v>173</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>398</v>
+        <v>174</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7478,7 +7494,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7512,7 +7528,7 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>400</v>
@@ -7520,7 +7536,9 @@
       <c r="M54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7545,13 +7563,13 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>75</v>
+        <v>402</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>75</v>
+        <v>403</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -7575,7 +7593,7 @@
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>96</v>
@@ -7584,7 +7602,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7592,10 +7610,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7618,17 +7636,15 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7677,13 +7693,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>96</v>
@@ -7692,7 +7708,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7714,7 +7730,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7726,15 +7742,17 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>101</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7783,22 +7801,22 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>103</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7806,21 +7824,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -7832,17 +7850,15 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7879,34 +7895,34 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7914,14 +7930,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7934,26 +7950,24 @@
         <v>75</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -7989,19 +8003,19 @@
         <v>75</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>114</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8024,14 +8038,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8044,24 +8058,26 @@
         <v>75</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8085,13 +8101,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>413</v>
+        <v>75</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8109,7 +8125,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>372</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8121,10 +8137,10 @@
         <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>406</v>
+        <v>98</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8146,7 +8162,7 @@
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8158,7 +8174,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>277</v>
+        <v>168</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>416</v>
@@ -8166,7 +8182,9 @@
       <c r="M60" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="N60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8191,13 +8209,13 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>75</v>
+        <v>418</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>75</v>
+        <v>419</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8221,7 +8239,7 @@
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>96</v>
@@ -8230,7 +8248,7 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8238,10 +8256,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8264,17 +8282,15 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>419</v>
+        <v>282</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N61" t="s" s="2">
         <v>422</v>
       </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8323,7 +8339,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8338,7 +8354,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8372,16 +8388,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8446,7 +8462,7 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8454,10 +8470,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8468,7 +8484,7 @@
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -8480,15 +8496,17 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>358</v>
+        <v>424</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -8537,13 +8555,13 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>96</v>
@@ -8552,7 +8570,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8560,10 +8578,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8574,7 +8592,7 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
@@ -8586,13 +8604,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>101</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>102</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8643,22 +8661,22 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>103</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8666,21 +8684,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
@@ -8692,17 +8710,15 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8739,34 +8755,34 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8774,14 +8790,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8794,26 +8810,24 @@
         <v>75</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O66" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
       </c>
@@ -8849,19 +8863,19 @@
         <v>75</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>114</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8884,44 +8898,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>370</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>371</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -8969,22 +8985,22 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8992,10 +9008,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9003,7 +9019,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>84</v>
@@ -9018,16 +9034,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9077,10 +9093,10 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>84</v>
@@ -9089,10 +9105,10 @@
         <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>265</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>104</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9100,10 +9116,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9114,7 +9130,7 @@
         <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>75</v>
@@ -9126,16 +9142,16 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9185,7 +9201,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9197,10 +9213,10 @@
         <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9208,10 +9224,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9234,16 +9250,16 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>100</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9293,29 +9309,137 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL70">
+  <autoFilter ref="A1:AL71">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9325,7 +9449,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -390,7 +390,171 @@
     <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source.</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:autorite-enregistrement</t>
+  </si>
+  <si>
+    <t>autorite-enregistrement</t>
+  </si>
+  <si>
+    <t>Autorité d'enregistrement de la ressource.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:autorite-enregistrement.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.extension.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:autorite-enregistrement.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:autorite-enregistrement.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.extension.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:autorite-enregistrement.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:systeme-information</t>
+  </si>
+  <si>
+    <t>systeme-information</t>
+  </si>
+  <si>
+    <t>Système d'information de la ressource.</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:systeme-information.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:systeme-information.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:systeme-information.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:systeme-information.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>RPPS | ADELI | FINESS | MSS | CG</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae</t>
+  </si>
+  <si>
+    <t>date-maj-ae</t>
+  </si>
+  <si>
+    <t>Date maj de l'activité selon l'autorité d'enregistrement</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension:as-ext-data-trace.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>HealthcareService.meta.versionId</t>
@@ -430,10 +594,6 @@
     <t>HealthcareService.meta.source</t>
   </si>
   <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
@@ -482,9 +642,6 @@
     <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
@@ -537,10 +694,6 @@
   </si>
   <si>
     <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
   </si>
   <si>
     <t>Language of the resource content</t>
@@ -735,9 +888,6 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
@@ -754,10 +904,6 @@
   </si>
   <si>
     <t>HealthcareService.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Description of identifier</t>
@@ -1736,12 +1882,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL71"/>
+  <dimension ref="A1:AL90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.46484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.67578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="91.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.84765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.13671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1749,7 +1895,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2541,7 +2687,7 @@
         <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2561,20 +2707,18 @@
         <v>75</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>124</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -2623,7 +2767,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2632,10 +2776,10 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>104</v>
@@ -2646,21 +2790,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -2669,19 +2813,19 @@
         <v>75</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2719,34 +2863,34 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2754,12 +2898,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
@@ -2777,20 +2923,18 @@
         <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2839,22 +2983,22 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2862,10 +3006,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2876,7 +3020,7 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2885,20 +3029,18 @@
         <v>75</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2947,19 +3089,19 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>104</v>
@@ -2970,10 +3112,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2984,7 +3126,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2993,20 +3135,18 @@
         <v>75</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>75</v>
@@ -3031,31 +3171,31 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3067,10 +3207,10 @@
         <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3078,10 +3218,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3089,10 +3229,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>75</v>
@@ -3101,19 +3241,19 @@
         <v>75</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3121,7 +3261,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>75</v>
@@ -3139,13 +3279,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -3163,22 +3303,22 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3186,10 +3326,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3206,23 +3346,21 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -3247,13 +3385,11 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -3271,7 +3407,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3286,7 +3422,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3294,12 +3430,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
@@ -3320,17 +3458,15 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>75</v>
@@ -3355,13 +3491,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3379,22 +3515,22 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3402,14 +3538,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3428,17 +3564,15 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>75</v>
@@ -3487,7 +3621,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3496,13 +3630,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3510,21 +3644,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -3536,17 +3670,15 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>75</v>
@@ -3583,19 +3715,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3604,13 +3736,13 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3618,21 +3750,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -3644,16 +3776,16 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3661,7 +3793,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>75</v>
@@ -3691,31 +3823,31 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>98</v>
@@ -3726,14 +3858,12 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>75</v>
       </c>
@@ -3742,10 +3872,10 @@
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -3754,13 +3884,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3787,13 +3917,11 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3811,22 +3939,22 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -3834,13 +3962,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>75</v>
@@ -3850,7 +3978,7 @@
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>85</v>
@@ -3862,13 +3990,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3919,7 +4047,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3942,46 +4070,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
@@ -4017,34 +4141,34 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>103</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>75</v>
@@ -4052,10 +4176,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4066,7 +4190,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -4075,16 +4199,16 @@
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>210</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4123,10 +4247,10 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
@@ -4135,7 +4259,7 @@
         <v>113</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4147,61 +4271,61 @@
         <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>75</v>
@@ -4243,33 +4367,33 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4292,13 +4416,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4349,7 +4473,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4358,13 +4482,13 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4372,21 +4496,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>75</v>
@@ -4398,16 +4522,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4415,7 +4539,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>75</v>
@@ -4445,31 +4569,31 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>98</v>
@@ -4480,10 +4604,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4494,32 +4618,28 @@
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>144</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4543,13 +4663,13 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4567,7 +4687,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4582,7 +4702,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>98</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4590,10 +4710,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4616,20 +4736,18 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4653,13 +4771,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>242</v>
+        <v>75</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4677,7 +4795,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4692,7 +4810,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>234</v>
+        <v>104</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4700,10 +4818,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4711,7 +4829,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>84</v>
@@ -4726,20 +4844,18 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4748,10 +4864,10 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>251</v>
+        <v>75</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -4787,7 +4903,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4802,7 +4918,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4810,10 +4926,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4836,16 +4952,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4859,7 +4975,7 @@
         <v>75</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>75</v>
@@ -4895,7 +5011,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>189</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4910,7 +5026,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>104</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4918,10 +5034,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4932,7 +5048,7 @@
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4944,16 +5060,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>192</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5003,22 +5119,22 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -5026,10 +5142,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5040,7 +5156,7 @@
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -5052,16 +5168,16 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>200</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5087,13 +5203,13 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -5111,22 +5227,22 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>203</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>75</v>
@@ -5134,10 +5250,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5148,36 +5264,34 @@
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>197</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>207</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>208</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>75</v>
       </c>
@@ -5197,13 +5311,13 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>75</v>
+        <v>211</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -5221,13 +5335,13 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>96</v>
@@ -5236,18 +5350,18 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5261,25 +5375,25 @@
         <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>214</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5329,7 +5443,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5341,10 +5455,10 @@
         <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>294</v>
+        <v>104</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
@@ -5352,42 +5466,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>296</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>219</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5413,11 +5527,13 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5435,13 +5551,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>96</v>
@@ -5450,29 +5566,29 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -5481,19 +5597,19 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5519,11 +5635,13 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5541,13 +5659,13 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>96</v>
@@ -5556,7 +5674,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5564,42 +5682,42 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>311</v>
-      </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>307</v>
+        <v>239</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5625,11 +5743,13 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5647,7 +5767,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5656,13 +5776,13 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>98</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
@@ -5670,21 +5790,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -5693,19 +5813,19 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>315</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>108</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>318</v>
+        <v>110</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5743,19 +5863,19 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5767,23 +5887,25 @@
         <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>319</v>
+        <v>98</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>320</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5792,29 +5914,27 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>100</v>
+        <v>246</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>247</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5863,22 +5983,22 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5886,12 +6006,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
@@ -5900,29 +6022,27 @@
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>100</v>
+        <v>251</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5971,22 +6091,22 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5994,44 +6114,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>332</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>255</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>256</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -6067,34 +6189,34 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>258</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>98</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6102,10 +6224,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>259</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>259</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6116,7 +6238,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -6128,17 +6250,15 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>260</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>339</v>
+        <v>261</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6175,47 +6295,49 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>259</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>342</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>265</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>75</v>
       </c>
@@ -6224,29 +6346,27 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>260</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>269</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6295,7 +6415,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>259</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6307,21 +6427,21 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>349</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>270</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6332,7 +6452,7 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6344,17 +6464,15 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>315</v>
+        <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>101</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6403,22 +6521,22 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>103</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6426,21 +6544,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>272</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -6452,16 +6570,16 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>109</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>359</v>
+        <v>110</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6487,31 +6605,31 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>358</v>
+        <v>75</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6523,10 +6641,10 @@
         <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>361</v>
+        <v>98</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6534,10 +6652,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>275</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6548,28 +6666,32 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>156</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6593,13 +6715,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>75</v>
+        <v>281</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6617,13 +6739,13 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>282</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>96</v>
@@ -6632,7 +6754,7 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6640,10 +6762,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>285</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6663,19 +6785,23 @@
         <v>75</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>101</v>
+        <v>286</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -6699,13 +6825,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6723,7 +6849,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6732,13 +6858,13 @@
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6746,21 +6872,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>293</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -6769,21 +6895,23 @@
         <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>108</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>109</v>
+        <v>296</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -6792,10 +6920,10 @@
         <v>75</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -6819,34 +6947,34 @@
         <v>75</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>114</v>
+        <v>301</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>98</v>
+        <v>302</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6854,46 +6982,44 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>370</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>371</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6905,7 +7031,7 @@
         <v>75</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>75</v>
@@ -6941,22 +7067,22 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>98</v>
+        <v>310</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6964,10 +7090,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6987,19 +7113,19 @@
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7025,10 +7151,10 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>376</v>
+        <v>75</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>75</v>
@@ -7049,7 +7175,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7061,10 +7187,10 @@
         <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -7072,10 +7198,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7095,19 +7221,19 @@
         <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>324</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>325</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7157,7 +7283,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7169,10 +7295,10 @@
         <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>327</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7180,10 +7306,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7194,34 +7320,36 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>237</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="R51" t="s" s="2">
         <v>75</v>
       </c>
@@ -7241,13 +7369,13 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>386</v>
+        <v>75</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>387</v>
+        <v>75</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7265,13 +7393,13 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>96</v>
@@ -7280,18 +7408,18 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>75</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7302,7 +7430,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>85</v>
@@ -7311,19 +7439,19 @@
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7349,11 +7477,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>393</v>
+        <v>75</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7371,22 +7501,22 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>337</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>327</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>388</v>
+        <v>342</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7394,42 +7524,42 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>237</v>
+        <v>143</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>395</v>
+        <v>345</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>396</v>
+        <v>346</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7455,13 +7585,11 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>174</v>
+        <v>348</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7479,7 +7607,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7494,29 +7622,29 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7525,19 +7653,19 @@
         <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>237</v>
+        <v>143</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7563,13 +7691,11 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -7587,7 +7713,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7602,7 +7728,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7610,10 +7736,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7627,24 +7753,26 @@
         <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>143</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>359</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7669,13 +7797,11 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7693,13 +7819,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>96</v>
@@ -7708,7 +7834,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7716,10 +7842,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7739,19 +7865,19 @@
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>363</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>408</v>
+        <v>364</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>409</v>
+        <v>365</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7801,7 +7927,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7813,21 +7939,21 @@
         <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>327</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>411</v>
+        <v>367</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>75</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7838,7 +7964,7 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -7847,18 +7973,20 @@
         <v>75</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>101</v>
+        <v>370</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7907,7 +8035,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>103</v>
+        <v>369</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7916,13 +8044,13 @@
         <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>104</v>
+        <v>373</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7930,21 +8058,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
@@ -7953,19 +8081,19 @@
         <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>108</v>
+        <v>375</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>109</v>
+        <v>376</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>110</v>
+        <v>377</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8003,34 +8131,34 @@
         <v>75</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>114</v>
+        <v>374</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>378</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -8038,46 +8166,44 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8125,22 +8251,22 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>98</v>
+        <v>384</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8148,10 +8274,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8162,7 +8288,7 @@
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8171,19 +8297,19 @@
         <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>168</v>
+        <v>386</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8209,13 +8335,13 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>418</v>
+        <v>75</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>419</v>
+        <v>75</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8233,22 +8359,22 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>390</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8256,10 +8382,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8270,7 +8396,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -8282,15 +8408,17 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>282</v>
+        <v>393</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8339,22 +8467,22 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8362,10 +8490,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8376,7 +8504,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -8388,16 +8516,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>424</v>
+        <v>363</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8447,22 +8575,22 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>327</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8470,10 +8598,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8484,7 +8612,7 @@
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -8496,16 +8624,16 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>424</v>
+        <v>143</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8531,13 +8659,13 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>75</v>
+        <v>406</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>408</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -8555,13 +8683,13 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>96</v>
@@ -8570,7 +8698,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8578,10 +8706,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8604,13 +8732,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8661,7 +8789,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8676,7 +8804,7 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>411</v>
+        <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8684,10 +8812,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8790,10 +8918,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8898,14 +9026,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -8927,16 +9055,16 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>207</v>
+        <v>257</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8985,7 +9113,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9008,10 +9136,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9019,7 +9147,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>84</v>
@@ -9034,16 +9162,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9069,10 +9197,10 @@
         <v>75</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>75</v>
+        <v>424</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>75</v>
@@ -9093,10 +9221,10 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>84</v>
@@ -9108,7 +9236,7 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>104</v>
+        <v>409</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9116,10 +9244,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9142,16 +9270,16 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>265</v>
+        <v>380</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>268</v>
+        <v>428</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9201,7 +9329,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9213,10 +9341,10 @@
         <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9224,10 +9352,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9250,16 +9378,16 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>324</v>
+        <v>433</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9285,13 +9413,13 @@
         <v>75</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>75</v>
+        <v>434</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -9309,13 +9437,13 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>96</v>
@@ -9324,7 +9452,7 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>
@@ -9332,10 +9460,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9346,10 +9474,10 @@
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
@@ -9358,16 +9486,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>447</v>
+        <v>143</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>318</v>
+        <v>440</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9393,13 +9521,11 @@
         <v>75</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>75</v>
@@ -9417,7 +9543,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9429,17 +9555,2063 @@
         <v>96</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="Z73" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL71">
+  <autoFilter ref="A1:AL90">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9449,7 +11621,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
